--- a/src/main/resources/testdata/DataTest_Login.xlsx
+++ b/src/main/resources/testdata/DataTest_Login.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ProjectAETesting\AETesting\src\main\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC20C600-0226-49C4-82A5-86BE5DE214E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C90A4F7-63DB-4397-838F-F749FB2D07E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
